--- a/Tools/config/excel/config.xlsx
+++ b/Tools/config/excel/config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="14900" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Navigator" sheetId="2" r:id="rId1"/>
@@ -1193,14 +1193,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="5.925" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.08333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.45" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.92307692307692" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08653846153846" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.45192307692308" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.05" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.04807692307692" style="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -2028,12 +2028,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="5.925" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.08333333333333" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.08333333333333" style="3" customWidth="1"/>
-    <col min="4" max="4" width="35.3833333333333" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.92307692307692" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.08653846153846" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.08653846153846" style="3" customWidth="1"/>
+    <col min="4" max="4" width="35.3846153846154" style="3" customWidth="1"/>
     <col min="5" max="5" width="35.75" style="3" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
